--- a/data/trans_camb/IP19C06-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP19C06-Edad-trans_camb.xlsx
@@ -893,22 +893,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,4</t>
+          <t>0,0; 3,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,62</t>
+          <t>0,0; 6,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,76</t>
+          <t>0,0; 5,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,11</t>
+          <t>0,0; 3,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -918,22 +918,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,68</t>
+          <t>0,0; 7,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,74</t>
+          <t>0,0; 2,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,57</t>
+          <t>0,0; 3,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 5,0</t>
+          <t>0,27; 4,39</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,56</t>
+          <t>0,0; 2,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,01</t>
+          <t>0,55; 5,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,36</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,25</t>
+          <t>0,26; 2,43</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,85</t>
+          <t>0,29; 4,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,18</t>
+          <t>0,0; 2,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,99</t>
+          <t>0,36; 3,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 2,75</t>
+          <t>-1,09; 2,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 1,26</t>
+          <t>-1,49; 1,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 1,62</t>
+          <t>-1,46; 1,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 2,24</t>
+          <t>-0,07; 2,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 1,21</t>
+          <t>-0,52; 1,31</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 1,63</t>
+          <t>-0,36; 1,58</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,0</t>
+          <t>0,32; 2,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,49</t>
+          <t>0,0; 1,28</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,66</t>
+          <t>0,68; 2,68</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,35</t>
+          <t>-0,48; 1,32</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 0,38</t>
+          <t>-0,86; 0,38</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 1,17</t>
+          <t>-0,51; 1,22</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,21</t>
+          <t>0,1; 1,26</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 0,59</t>
+          <t>-0,21; 0,55</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,42</t>
+          <t>0,22; 1,5</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-61,01; —</t>
+          <t>-38,5; —</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-8,7; —</t>
+          <t>-13,05; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C06-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP19C06-Edad-trans_camb.xlsx
@@ -893,22 +893,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,77</t>
+          <t>0,0; 3,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,46</t>
+          <t>0,0; 5,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,1</t>
+          <t>0,0; 5,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,67</t>
+          <t>0,0; 4,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -918,22 +918,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,21</t>
+          <t>0,0; 6,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,75</t>
+          <t>0,0; 2,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,1</t>
+          <t>0,0; 2,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 4,39</t>
+          <t>0,27; 4,4</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,47</t>
+          <t>0,0; 2,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,02</t>
+          <t>0,56; 4,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,52</t>
+          <t>0,0; 1,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,43</t>
+          <t>0,23; 2,2</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,29; 4,1</t>
+          <t>0,29; 4,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,38</t>
+          <t>0,0; 2,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,11</t>
+          <t>0,35; 2,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 2,57</t>
+          <t>-1,1; 2,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 1,5</t>
+          <t>-1,49; 1,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 1,65</t>
+          <t>-1,3; 1,68</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 2,18</t>
+          <t>-0,16; 2,2</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 1,31</t>
+          <t>-0,61; 1,12</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 1,58</t>
+          <t>-0,42; 1,58</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,07</t>
+          <t>0,32; 2,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,28</t>
+          <t>0,0; 1,37</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,68</t>
+          <t>0,71; 2,83</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 1,32</t>
+          <t>-0,46; 1,3</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,38</t>
+          <t>-0,87; 0,38</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,22</t>
+          <t>-0,53; 1,19</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,26</t>
+          <t>0,1; 1,28</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 0,55</t>
+          <t>-0,24; 0,59</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,5</t>
+          <t>0,2; 1,53</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-38,5; —</t>
+          <t>-57,42; —</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-13,05; —</t>
+          <t>-19,06; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C06-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP19C06-Edad-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,81</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,43</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,75</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1,13</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,41</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,81</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,35</t>
+          <t>1,29</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,38</t>
+          <t>1,36</t>
         </is>
       </c>
     </row>
@@ -893,37 +893,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,7</t>
+          <t>0,0; 4,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,8</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,02</t>
+          <t>0,0; 7,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,15</t>
+          <t>0,0; 4,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,16</t>
+          <t>0,0; 4,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,66</t>
+          <t>0,0; 2,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 4,4</t>
+          <t>0,27; 5,01</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,56</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2,11</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>2,06</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 4,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,55; 5,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,37</t>
+          <t>0,0; 1,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,2</t>
+          <t>0,27; 2,25</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,35</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,18</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-0,43</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1,32</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,43</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1,14</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,35</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,18</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,14</t>
+          <t>1,15</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,32</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,29; 4,14</t>
+          <t>-1,01; 2,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,2</t>
+          <t>-1,42; 1,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,98</t>
+          <t>-1,93; 0,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 2,5</t>
+          <t>0,29; 3,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 1,35</t>
+          <t>0,0; 2,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 1,68</t>
+          <t>0,37; 3,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 2,2</t>
+          <t>-0,2; 2,24</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 1,12</t>
+          <t>-0,57; 1,21</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 1,58</t>
+          <t>-0,43; 1,2</t>
         </is>
       </c>
     </row>
@@ -1378,34 +1378,34 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>49,42%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-26,31%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-60,92%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>49,42%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-26,31%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-20,01%</t>
-        </is>
-      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
           <t>228,13%</t>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>128,28%</t>
+          <t>89,41%</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,27</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,15</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0,01</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>0,91</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>0,38</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1,47</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,27</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-0,15</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>1,44</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>0,68</t>
         </is>
       </c>
     </row>
@@ -1541,37 +1541,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,06</t>
+          <t>-0,44; 1,35</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,37</t>
+          <t>-0,82; 0,38</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,83</t>
+          <t>-0,58; 0,71</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 1,3</t>
+          <t>0,32; 2,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 0,38</t>
+          <t>0,0; 1,49</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 1,19</t>
+          <t>0,7; 2,64</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,28</t>
+          <t>0,11; 1,21</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,53</t>
+          <t>0,17; 1,28</t>
         </is>
       </c>
     </row>
@@ -1594,34 +1594,34 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>80,15%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-43,6%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>3,25%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>80,15%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-43,6%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>45,55%</t>
-        </is>
-      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
           <t>342,58%</t>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>442,67%</t>
+          <t>397,19%</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-57,42; —</t>
+          <t>-61,01; —</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-19,06; —</t>
+          <t>-18,61; —</t>
         </is>
       </c>
     </row>
